--- a/exports/CAS_Zoho_Import_Template.xlsx
+++ b/exports/CAS_Zoho_Import_Template.xlsx
@@ -399,32 +399,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:W1"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
     <col min="13" max="13" width="30.83203125" customWidth="1"/>
-    <col min="14" max="14" width="30.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="19.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
     <col min="17" max="17" width="16.83203125" customWidth="1"/>
     <col min="18" max="18" width="16.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
-    <col min="21" max="21" width="20.83203125" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" customWidth="1"/>
-    <col min="23" max="23" width="23.83203125" customWidth="1"/>
-    <col min="24" max="24" width="24.83203125" customWidth="1"/>
+    <col min="19" max="19" width="19.83203125" customWidth="1"/>
+    <col min="20" max="20" width="20.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="23.83203125" customWidth="1"/>
+    <col min="23" max="23" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,76 +440,73 @@
         <v>Secondary Email</v>
       </c>
       <c r="E1" t="str">
-        <v>Salutation</v>
+        <v>Professional Designation</v>
       </c>
       <c r="F1" t="str">
-        <v>Professional Designation</v>
+        <v>Subspecialty</v>
       </c>
       <c r="G1" t="str">
-        <v>Subspecialty</v>
+        <v>Institution (Company)</v>
       </c>
       <c r="H1" t="str">
-        <v>Institution</v>
+        <v>Amyloidosis Type</v>
       </c>
       <c r="I1" t="str">
-        <v>Amyloidosis Type</v>
+        <v>Amyloidosis Type - Other</v>
       </c>
       <c r="J1" t="str">
-        <v>Amyloidosis Type - Other</v>
+        <v>CAS Member</v>
       </c>
       <c r="K1" t="str">
-        <v>CAS Member</v>
+        <v>CANN Member</v>
       </c>
       <c r="L1" t="str">
-        <v>CANN Member</v>
+        <v>CAS Communications Consent</v>
       </c>
       <c r="M1" t="str">
-        <v>CAS Communications Consent</v>
+        <v>CANN Communications Consent</v>
       </c>
       <c r="N1" t="str">
-        <v>CANN Communications Consent</v>
+        <v>Services Map Inclusion</v>
       </c>
       <c r="O1" t="str">
-        <v>Services Map Inclusion</v>
+        <v>Map Clinic Name</v>
       </c>
       <c r="P1" t="str">
-        <v>Map Clinic Name</v>
+        <v>Map Street</v>
       </c>
       <c r="Q1" t="str">
-        <v>Map Street</v>
+        <v>Map City</v>
       </c>
       <c r="R1" t="str">
-        <v>Map City</v>
+        <v>Map Province</v>
       </c>
       <c r="S1" t="str">
-        <v>Map Province</v>
+        <v>Map Postal Code</v>
       </c>
       <c r="T1" t="str">
-        <v>Map Postal Code</v>
+        <v>Map Clinic Phone</v>
       </c>
       <c r="U1" t="str">
-        <v>Map Clinic Phone</v>
+        <v>Map Clinic Fax</v>
       </c>
       <c r="V1" t="str">
-        <v>Map Clinic Fax</v>
+        <v>Description / Notes</v>
       </c>
       <c r="W1" t="str">
-        <v>Description / Notes</v>
-      </c>
-      <c r="X1" t="str">
         <v>Form Submission Date</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -590,91 +586,91 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Salutation</v>
+        <v>Professional Designation</v>
       </c>
       <c r="B6" t="str">
-        <v>Optional</v>
+        <v>Required for members</v>
       </c>
       <c r="C6" t="str">
-        <v>Dr., Prof., Mr., Mrs., Ms., Mx.</v>
+        <v>Free text (e.g., Cardiology, Hematology, Neurology, Nephrology)</v>
       </c>
       <c r="D6" t="str">
-        <v>Title. The live form no longer asks this, but you can set it for imported records.</v>
+        <v>The person's discipline. -&gt; Zoho 'Professional Designation'.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Professional Designation</v>
+        <v>Subspecialty</v>
       </c>
       <c r="B7" t="str">
         <v>Required for members</v>
       </c>
       <c r="C7" t="str">
-        <v>Free text (e.g., Cardiology, Hematology, Neurology, Nephrology)</v>
+        <v>Free text</v>
       </c>
       <c r="D7" t="str">
-        <v>The person's discipline. -&gt; Zoho 'Professional Designation'.</v>
+        <v>Sub-specialty area. -&gt; Zoho 'subspecialty'.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Subspecialty</v>
+        <v>Institution (Company)</v>
       </c>
       <c r="B8" t="str">
-        <v>Required for members</v>
+        <v>Optional</v>
       </c>
       <c r="C8" t="str">
         <v>Free text</v>
       </c>
       <c r="D8" t="str">
-        <v>Sub-specialty area. -&gt; Zoho 'subspecialty'.</v>
+        <v>Clinic / centre / hospital name. -&gt; Zoho 'Institution (Company)'.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Institution</v>
+        <v>Amyloidosis Type</v>
       </c>
       <c r="B9" t="str">
-        <v>Optional</v>
+        <v>Required for members</v>
       </c>
       <c r="C9" t="str">
-        <v>Free text</v>
+        <v>ATTR | AL | Both ATTR and AL | Other</v>
       </c>
       <c r="D9" t="str">
-        <v>Clinic / centre / hospital name. -&gt; Zoho 'Company'.</v>
+        <v>Pick ONE exactly as written. If 'Other', fill the next column.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Amyloidosis Type</v>
+        <v>Amyloidosis Type - Other</v>
       </c>
       <c r="B10" t="str">
-        <v>Required for members</v>
+        <v>Required only if Type = Other</v>
       </c>
       <c r="C10" t="str">
-        <v>ATTR | AL | Both ATTR and AL | Other</v>
+        <v>Free text</v>
       </c>
       <c r="D10" t="str">
-        <v>Pick ONE exactly as written. If 'Other', fill the next column.</v>
+        <v>The specific type when Amyloidosis Type is 'Other'. -&gt; Zoho 'Amyloidosis_Type_Other'.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Amyloidosis Type - Other</v>
+        <v>CAS Member</v>
       </c>
       <c r="B11" t="str">
-        <v>Required only if Type = Other</v>
+        <v>Required</v>
       </c>
       <c r="C11" t="str">
-        <v>Free text</v>
+        <v>Yes | No</v>
       </c>
       <c r="D11" t="str">
-        <v>The specific type when Amyloidosis Type is 'Other'. -&gt; Zoho 'Amyloidosis_Type_Other'.</v>
+        <v>Is this person a CAS member? NOTE: if CANN Member = Yes, this is automatically forced to Yes.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CAS Member</v>
+        <v>CANN Member</v>
       </c>
       <c r="B12" t="str">
         <v>Required</v>
@@ -683,26 +679,26 @@
         <v>Yes | No</v>
       </c>
       <c r="D12" t="str">
-        <v>Is this person a CAS member? NOTE: if CANN Member = Yes, this is automatically forced to Yes.</v>
+        <v>Is this person a CANN member?</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CANN Member</v>
+        <v>CAS Communications Consent</v>
       </c>
       <c r="B13" t="str">
-        <v>Required</v>
+        <v>Optional</v>
       </c>
       <c r="C13" t="str">
         <v>Yes | No</v>
       </c>
       <c r="D13" t="str">
-        <v>Is this person a CANN member?</v>
+        <v>Did they opt in to CAS emails? -&gt; Zoho 'CAS_Communications'.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CAS Communications Consent</v>
+        <v>CANN Communications Consent</v>
       </c>
       <c r="B14" t="str">
         <v>Optional</v>
@@ -711,12 +707,12 @@
         <v>Yes | No</v>
       </c>
       <c r="D14" t="str">
-        <v>Did they opt in to CAS emails? -&gt; Zoho 'CAS_Communications'.</v>
+        <v>Did they opt in to CANN emails? -&gt; Zoho 'CANN_Communications'.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CANN Communications Consent</v>
+        <v>Services Map Inclusion</v>
       </c>
       <c r="B15" t="str">
         <v>Optional</v>
@@ -725,26 +721,26 @@
         <v>Yes | No</v>
       </c>
       <c r="D15" t="str">
-        <v>Did they opt in to CANN emails? -&gt; Zoho 'CANN_Communications'.</v>
+        <v>Include their clinic on the public services map? If 'No', leave the 7 Map columns blank.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Services Map Inclusion</v>
+        <v>Map Clinic Name</v>
       </c>
       <c r="B16" t="str">
-        <v>Optional</v>
+        <v>Only if Map = Yes</v>
       </c>
       <c r="C16" t="str">
-        <v>Yes | No</v>
+        <v>Free text</v>
       </c>
       <c r="D16" t="str">
-        <v>Include their clinic on the public services map? If 'No', leave the 7 Map columns blank.</v>
+        <v>Clinic/centre name to show on the map. -&gt; Zoho 'Map_Clinic_Name'.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Map Clinic Name</v>
+        <v>Map Street</v>
       </c>
       <c r="B17" t="str">
         <v>Only if Map = Yes</v>
@@ -753,12 +749,12 @@
         <v>Free text</v>
       </c>
       <c r="D17" t="str">
-        <v>Clinic/centre name to show on the map. -&gt; Zoho 'Map_Clinic_Name'.</v>
+        <v>Street address. -&gt; Zoho 'Map_Street'.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Map Street</v>
+        <v>Map City</v>
       </c>
       <c r="B18" t="str">
         <v>Only if Map = Yes</v>
@@ -767,110 +763,96 @@
         <v>Free text</v>
       </c>
       <c r="D18" t="str">
-        <v>Street address. -&gt; Zoho 'Map_Street'.</v>
+        <v>City. -&gt; Zoho 'Map_City'.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Map City</v>
+        <v>Map Province</v>
       </c>
       <c r="B19" t="str">
         <v>Only if Map = Yes</v>
       </c>
       <c r="C19" t="str">
-        <v>Free text</v>
+        <v>Alberta | British Columbia | Manitoba | New Brunswick | Newfoundland and Labrador | Northwest Territories | Nova Scotia | Nunavut | Ontario | Prince Edward Island | Quebec | Saskatchewan | Yukon</v>
       </c>
       <c r="D19" t="str">
-        <v>City. -&gt; Zoho 'Map_City'.</v>
+        <v>Full province name, spelled exactly. -&gt; Zoho 'Map_Province'.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Map Province</v>
+        <v>Map Postal Code</v>
       </c>
       <c r="B20" t="str">
         <v>Only if Map = Yes</v>
       </c>
       <c r="C20" t="str">
-        <v>Alberta | British Columbia | Manitoba | New Brunswick | Newfoundland and Labrador | Northwest Territories | Nova Scotia | Nunavut | Ontario | Prince Edward Island | Quebec | Saskatchewan | Yukon</v>
+        <v>Canadian postal code (e.g., M5H 2N2)</v>
       </c>
       <c r="D20" t="str">
-        <v>Full province name, spelled exactly. -&gt; Zoho 'Map_Province'.</v>
+        <v>Auto-uppercased on import. -&gt; Zoho 'Map_Postal_Code'.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Map Postal Code</v>
+        <v>Map Clinic Phone</v>
       </c>
       <c r="B21" t="str">
         <v>Only if Map = Yes</v>
       </c>
       <c r="C21" t="str">
-        <v>Canadian postal code (e.g., M5H 2N2)</v>
+        <v>10 digits incl. area code</v>
       </c>
       <c r="D21" t="str">
-        <v>Auto-uppercased on import. -&gt; Zoho 'Map_Postal_Code'.</v>
+        <v>-&gt; Zoho 'Map_Clinic_Phone'.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Map Clinic Phone</v>
+        <v>Map Clinic Fax</v>
       </c>
       <c r="B22" t="str">
-        <v>Only if Map = Yes</v>
+        <v>Optional (Map = Yes)</v>
       </c>
       <c r="C22" t="str">
         <v>10 digits incl. area code</v>
       </c>
       <c r="D22" t="str">
-        <v>-&gt; Zoho 'Map_Clinic_Phone'.</v>
+        <v>-&gt; Zoho 'Map_Clinic_Fax'.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Map Clinic Fax</v>
+        <v>Description / Notes</v>
       </c>
       <c r="B23" t="str">
-        <v>Optional (Map = Yes)</v>
+        <v>Optional</v>
       </c>
       <c r="C23" t="str">
-        <v>10 digits incl. area code</v>
+        <v>Free text</v>
       </c>
       <c r="D23" t="str">
-        <v>-&gt; Zoho 'Map_Clinic_Fax'.</v>
+        <v>Inquiry message or any notes. -&gt; Zoho 'Description'. Mainly for non-members.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Description / Notes</v>
+        <v>Form Submission Date</v>
       </c>
       <c r="B24" t="str">
         <v>Optional</v>
       </c>
       <c r="C24" t="str">
-        <v>Free text</v>
+        <v>YYYY-MM-DD or full date</v>
       </c>
       <c r="D24" t="str">
-        <v>Inquiry message or any notes. -&gt; Zoho 'Description'. Mainly for non-members.</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Form Submission Date</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="C25" t="str">
-        <v>YYYY-MM-DD or full date</v>
-      </c>
-      <c r="D25" t="str">
         <v>When they originally signed up. If blank, import time is used. -&gt; Zoho 'Form_Submission_Date'.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -949,7 +931,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">  - Member rows: fill First Name, Last Name, Primary Email, Professional Designation, Subspecialty, Amyloidosis Type, Institution.</v>
+        <v xml:space="preserve">  - Member rows: fill First Name, Last Name, Primary Email, Professional Designation, Subspecialty, Amyloidosis Type, Institution (Company).</v>
       </c>
     </row>
     <row r="15">
